--- a/tame_output/ON/bt/strategyON_20230827.xlsx
+++ b/tame_output/ON/bt/strategyON_20230827.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.2%</t>
         </is>
       </c>
     </row>
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.5%</t>
+          <t>454.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.0%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.8%</t>
+          <t>-158.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.7%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1701"/>
+  <dimension ref="A1:G1702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40633,7 +40633,7 @@
         <v>45163</v>
       </c>
       <c r="B1701" t="n">
-        <v>2.770093262391005</v>
+        <v>2.769822060368481</v>
       </c>
       <c r="C1701" t="n">
         <v>2.897971724056924</v>
@@ -40649,6 +40649,29 @@
       </c>
       <c r="G1701" t="n">
         <v>4.19540386263396</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="2" t="n">
+        <v>45164</v>
+      </c>
+      <c r="B1702" t="n">
+        <v>2.767126481393998</v>
+      </c>
+      <c r="C1702" t="n">
+        <v>2.89915643750998</v>
+      </c>
+      <c r="D1702" t="n">
+        <v>1.543766031472192</v>
+      </c>
+      <c r="E1702" t="n">
+        <v>3.51630642578511</v>
+      </c>
+      <c r="F1702" t="n">
+        <v>2.162933505552152</v>
+      </c>
+      <c r="G1702" t="n">
+        <v>4.196916540841273</v>
       </c>
     </row>
   </sheetData>
